--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -11521,7 +11521,7 @@
     </row>
     <row r="419">
       <c r="A419" s="1" t="n">
-        <v>45940.5358449074</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B419" t="n">
         <v>300</v>
@@ -11542,6 +11542,32 @@
         <v>37</v>
       </c>
       <c r="H419" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="n">
+        <v>45943.62625</v>
+      </c>
+      <c r="B420" t="n">
+        <v>13800</v>
+      </c>
+      <c r="C420" t="n">
+        <v>6.23999977111816</v>
+      </c>
+      <c r="D420" t="n">
+        <v>6.15999984741211</v>
+      </c>
+      <c r="E420" t="n">
+        <v>6.17999982833862</v>
+      </c>
+      <c r="F420" t="n">
+        <v>6.23999977111816</v>
+      </c>
+      <c r="G420" t="s">
+        <v>45</v>
+      </c>
+      <c r="H420" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -11547,7 +11547,7 @@
     </row>
     <row r="420">
       <c r="A420" s="1" t="n">
-        <v>45943.62625</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B420" t="n">
         <v>13800</v>
@@ -11568,6 +11568,32 @@
         <v>45</v>
       </c>
       <c r="H420" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="n">
+        <v>45944.473125</v>
+      </c>
+      <c r="B421" t="n">
+        <v>2700</v>
+      </c>
+      <c r="C421" t="n">
+        <v>6.21999979019165</v>
+      </c>
+      <c r="D421" t="n">
+        <v>6.15999984741211</v>
+      </c>
+      <c r="E421" t="n">
+        <v>6.21999979019165</v>
+      </c>
+      <c r="F421" t="n">
+        <v>6.15999984741211</v>
+      </c>
+      <c r="G421" t="s">
+        <v>37</v>
+      </c>
+      <c r="H421" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -11573,7 +11573,7 @@
     </row>
     <row r="421">
       <c r="A421" s="1" t="n">
-        <v>45944.473125</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B421" t="n">
         <v>2700</v>
@@ -11594,6 +11594,32 @@
         <v>37</v>
       </c>
       <c r="H421" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="n">
+        <v>45945.5984375</v>
+      </c>
+      <c r="B422" t="n">
+        <v>4200</v>
+      </c>
+      <c r="C422" t="n">
+        <v>6.32000017166138</v>
+      </c>
+      <c r="D422" t="n">
+        <v>6.21999979019165</v>
+      </c>
+      <c r="E422" t="n">
+        <v>6.21999979019165</v>
+      </c>
+      <c r="F422" t="n">
+        <v>6.30000019073486</v>
+      </c>
+      <c r="G422" t="s">
+        <v>50</v>
+      </c>
+      <c r="H422" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -11599,7 +11599,7 @@
     </row>
     <row r="422">
       <c r="A422" s="1" t="n">
-        <v>45945.5984375</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B422" t="n">
         <v>4200</v>
@@ -11620,6 +11620,32 @@
         <v>50</v>
       </c>
       <c r="H422" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="1" t="n">
+        <v>45946.6225462963</v>
+      </c>
+      <c r="B423" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C423" t="n">
+        <v>6.26000022888184</v>
+      </c>
+      <c r="D423" t="n">
+        <v>6.17999982833862</v>
+      </c>
+      <c r="E423" t="n">
+        <v>6.17999982833862</v>
+      </c>
+      <c r="F423" t="n">
+        <v>6.26000022888184</v>
+      </c>
+      <c r="G423" t="s">
+        <v>51</v>
+      </c>
+      <c r="H423" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -11625,7 +11625,7 @@
     </row>
     <row r="423">
       <c r="A423" s="1" t="n">
-        <v>45946.6225462963</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B423" t="n">
         <v>1200</v>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -11649,6 +11649,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="424">
+      <c r="A424" s="1" t="n">
+        <v>45947.2916666667</v>
+      </c>
+      <c r="B424" t="n">
+        <v>0</v>
+      </c>
+      <c r="C424" t="n">
+        <v>6.26000022888184</v>
+      </c>
+      <c r="D424" t="n">
+        <v>6.26000022888184</v>
+      </c>
+      <c r="E424" t="n">
+        <v>6.26000022888184</v>
+      </c>
+      <c r="F424" t="n">
+        <v>6.26000022888184</v>
+      </c>
+      <c r="G424" t="s">
+        <v>51</v>
+      </c>
+      <c r="H424" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="n">
+        <v>45950.5977430556</v>
+      </c>
+      <c r="B425" t="n">
+        <v>3600</v>
+      </c>
+      <c r="C425" t="n">
+        <v>6.28000020980835</v>
+      </c>
+      <c r="D425" t="n">
+        <v>6.17999982833862</v>
+      </c>
+      <c r="E425" t="n">
+        <v>6.26000022888184</v>
+      </c>
+      <c r="F425" t="n">
+        <v>6.17999982833862</v>
+      </c>
+      <c r="G425" t="s">
+        <v>59</v>
+      </c>
+      <c r="H425" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -11677,7 +11677,7 @@
     </row>
     <row r="425">
       <c r="A425" s="1" t="n">
-        <v>45950.5977430556</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B425" t="n">
         <v>3600</v>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -11701,6 +11701,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="426">
+      <c r="A426" s="1" t="n">
+        <v>45951.2916666667</v>
+      </c>
+      <c r="B426" t="n">
+        <v>0</v>
+      </c>
+      <c r="C426" t="n">
+        <v>6.17999982833862</v>
+      </c>
+      <c r="D426" t="n">
+        <v>6.17999982833862</v>
+      </c>
+      <c r="E426" t="n">
+        <v>6.17999982833862</v>
+      </c>
+      <c r="F426" t="n">
+        <v>6.17999982833862</v>
+      </c>
+      <c r="G426" t="s">
+        <v>59</v>
+      </c>
+      <c r="H426" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="n">
+        <v>45952.636099537</v>
+      </c>
+      <c r="B427" t="n">
+        <v>3600</v>
+      </c>
+      <c r="C427" t="n">
+        <v>6.21999979019165</v>
+      </c>
+      <c r="D427" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="E427" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="F427" t="n">
+        <v>6.21999979019165</v>
+      </c>
+      <c r="G427" t="s">
+        <v>53</v>
+      </c>
+      <c r="H427" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -11729,7 +11729,7 @@
     </row>
     <row r="427">
       <c r="A427" s="1" t="n">
-        <v>45952.636099537</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B427" t="n">
         <v>3600</v>
@@ -11750,6 +11750,32 @@
         <v>53</v>
       </c>
       <c r="H427" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="1" t="n">
+        <v>45953.5986226852</v>
+      </c>
+      <c r="B428" t="n">
+        <v>5700</v>
+      </c>
+      <c r="C428" t="n">
+        <v>6.1399998664856</v>
+      </c>
+      <c r="D428" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="E428" t="n">
+        <v>6.1399998664856</v>
+      </c>
+      <c r="F428" t="n">
+        <v>6.1399998664856</v>
+      </c>
+      <c r="G428" t="s">
+        <v>44</v>
+      </c>
+      <c r="H428" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -11755,7 +11755,7 @@
     </row>
     <row r="428">
       <c r="A428" s="1" t="n">
-        <v>45953.5986226852</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B428" t="n">
         <v>5700</v>
@@ -11776,6 +11776,32 @@
         <v>44</v>
       </c>
       <c r="H428" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="1" t="n">
+        <v>45954.4216898148</v>
+      </c>
+      <c r="B429" t="n">
+        <v>3900</v>
+      </c>
+      <c r="C429" t="n">
+        <v>6.1399998664856</v>
+      </c>
+      <c r="D429" t="n">
+        <v>6.11999988555908</v>
+      </c>
+      <c r="E429" t="n">
+        <v>6.1399998664856</v>
+      </c>
+      <c r="F429" t="n">
+        <v>6.1399998664856</v>
+      </c>
+      <c r="G429" t="s">
+        <v>44</v>
+      </c>
+      <c r="H429" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -11781,7 +11781,7 @@
     </row>
     <row r="429">
       <c r="A429" s="1" t="n">
-        <v>45954.4216898148</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B429" t="n">
         <v>3900</v>
@@ -11802,6 +11802,32 @@
         <v>44</v>
       </c>
       <c r="H429" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="1" t="n">
+        <v>45957.4771064815</v>
+      </c>
+      <c r="B430" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C430" t="n">
+        <v>6.15999984741211</v>
+      </c>
+      <c r="D430" t="n">
+        <v>6.1399998664856</v>
+      </c>
+      <c r="E430" t="n">
+        <v>6.1399998664856</v>
+      </c>
+      <c r="F430" t="n">
+        <v>6.1399998664856</v>
+      </c>
+      <c r="G430" t="s">
+        <v>44</v>
+      </c>
+      <c r="H430" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -11807,7 +11807,7 @@
     </row>
     <row r="430">
       <c r="A430" s="1" t="n">
-        <v>45957.4771064815</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B430" t="n">
         <v>2400</v>
@@ -11828,6 +11828,32 @@
         <v>44</v>
       </c>
       <c r="H430" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="n">
+        <v>45958.6683680556</v>
+      </c>
+      <c r="B431" t="n">
+        <v>4800</v>
+      </c>
+      <c r="C431" t="n">
+        <v>6.21999979019165</v>
+      </c>
+      <c r="D431" t="n">
+        <v>6.17999982833862</v>
+      </c>
+      <c r="E431" t="n">
+        <v>6.17999982833862</v>
+      </c>
+      <c r="F431" t="n">
+        <v>6.17999982833862</v>
+      </c>
+      <c r="G431" t="s">
+        <v>59</v>
+      </c>
+      <c r="H431" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -11833,7 +11833,7 @@
     </row>
     <row r="431">
       <c r="A431" s="1" t="n">
-        <v>45958.6683680556</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B431" t="n">
         <v>4800</v>
@@ -11854,6 +11854,32 @@
         <v>59</v>
       </c>
       <c r="H431" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="n">
+        <v>45959.6847337963</v>
+      </c>
+      <c r="B432" t="n">
+        <v>5100</v>
+      </c>
+      <c r="C432" t="n">
+        <v>6.28000020980835</v>
+      </c>
+      <c r="D432" t="n">
+        <v>6.1399998664856</v>
+      </c>
+      <c r="E432" t="n">
+        <v>6.17999982833862</v>
+      </c>
+      <c r="F432" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="G432" t="s">
+        <v>58</v>
+      </c>
+      <c r="H432" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -11859,7 +11859,7 @@
     </row>
     <row r="432">
       <c r="A432" s="1" t="n">
-        <v>45959.6847337963</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B432" t="n">
         <v>5100</v>
@@ -11880,6 +11880,32 @@
         <v>58</v>
       </c>
       <c r="H432" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="1" t="n">
+        <v>45960.6912615741</v>
+      </c>
+      <c r="B433" t="n">
+        <v>11100</v>
+      </c>
+      <c r="C433" t="n">
+        <v>6.32000017166138</v>
+      </c>
+      <c r="D433" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="E433" t="n">
+        <v>6.26000022888184</v>
+      </c>
+      <c r="F433" t="n">
+        <v>6.3600001335144</v>
+      </c>
+      <c r="G433" t="s">
+        <v>67</v>
+      </c>
+      <c r="H433" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -315,6 +315,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.55999994277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48000001907349</t>
   </si>
 </sst>
 </file>
@@ -11885,13 +11888,13 @@
     </row>
     <row r="433">
       <c r="A433" s="1" t="n">
-        <v>45960.6912615741</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B433" t="n">
         <v>11100</v>
       </c>
       <c r="C433" t="n">
-        <v>6.32000017166138</v>
+        <v>6.3600001335144</v>
       </c>
       <c r="D433" t="n">
         <v>6.19999980926514</v>
@@ -11906,6 +11909,32 @@
         <v>67</v>
       </c>
       <c r="H433" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="n">
+        <v>45961.6844097222</v>
+      </c>
+      <c r="B434" t="n">
+        <v>48300</v>
+      </c>
+      <c r="C434" t="n">
+        <v>6.71999979019165</v>
+      </c>
+      <c r="D434" t="n">
+        <v>6.38000011444092</v>
+      </c>
+      <c r="E434" t="n">
+        <v>6.38000011444092</v>
+      </c>
+      <c r="F434" t="n">
+        <v>6.48000001907349</v>
+      </c>
+      <c r="G434" t="s">
+        <v>101</v>
+      </c>
+      <c r="H434" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -11914,7 +11914,7 @@
     </row>
     <row r="434">
       <c r="A434" s="1" t="n">
-        <v>45961.6844097222</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B434" t="n">
         <v>48300</v>
@@ -11935,6 +11935,32 @@
         <v>101</v>
       </c>
       <c r="H434" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="1" t="n">
+        <v>45964.6909953704</v>
+      </c>
+      <c r="B435" t="n">
+        <v>5400</v>
+      </c>
+      <c r="C435" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D435" t="n">
+        <v>6.42000007629395</v>
+      </c>
+      <c r="E435" t="n">
+        <v>6.44000005722046</v>
+      </c>
+      <c r="F435" t="n">
+        <v>6.48000001907349</v>
+      </c>
+      <c r="G435" t="s">
+        <v>101</v>
+      </c>
+      <c r="H435" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -11940,7 +11940,7 @@
     </row>
     <row r="435">
       <c r="A435" s="1" t="n">
-        <v>45964.6909953704</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B435" t="n">
         <v>5400</v>
@@ -11961,6 +11961,32 @@
         <v>101</v>
       </c>
       <c r="H435" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="1" t="n">
+        <v>45965.6246064815</v>
+      </c>
+      <c r="B436" t="n">
+        <v>900</v>
+      </c>
+      <c r="C436" t="n">
+        <v>6.48000001907349</v>
+      </c>
+      <c r="D436" t="n">
+        <v>6.46000003814697</v>
+      </c>
+      <c r="E436" t="n">
+        <v>6.46000003814697</v>
+      </c>
+      <c r="F436" t="n">
+        <v>6.48000001907349</v>
+      </c>
+      <c r="G436" t="s">
+        <v>101</v>
+      </c>
+      <c r="H436" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -11966,7 +11966,7 @@
     </row>
     <row r="436">
       <c r="A436" s="1" t="n">
-        <v>45965.6246064815</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B436" t="n">
         <v>900</v>
@@ -11987,6 +11987,32 @@
         <v>101</v>
       </c>
       <c r="H436" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="1" t="n">
+        <v>45966.6048958333</v>
+      </c>
+      <c r="B437" t="n">
+        <v>12900</v>
+      </c>
+      <c r="C437" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D437" t="n">
+        <v>6.46000003814697</v>
+      </c>
+      <c r="E437" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F437" t="n">
+        <v>6.48000001907349</v>
+      </c>
+      <c r="G437" t="s">
+        <v>101</v>
+      </c>
+      <c r="H437" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -11992,19 +11992,19 @@
     </row>
     <row r="437">
       <c r="A437" s="1" t="n">
-        <v>45966.6048958333</v>
+        <v>45967.6489236111</v>
       </c>
       <c r="B437" t="n">
-        <v>12900</v>
+        <v>1500</v>
       </c>
       <c r="C437" t="n">
-        <v>6.5</v>
+        <v>6.48000001907349</v>
       </c>
       <c r="D437" t="n">
-        <v>6.46000003814697</v>
+        <v>6.48000001907349</v>
       </c>
       <c r="E437" t="n">
-        <v>6.5</v>
+        <v>6.48000001907349</v>
       </c>
       <c r="F437" t="n">
         <v>6.48000001907349</v>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -318,6 +318,9 @@
   </si>
   <si>
     <t xml:space="preserve">6.48000001907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55999994277954</t>
   </si>
 </sst>
 </file>
@@ -11992,25 +11995,25 @@
     </row>
     <row r="437">
       <c r="A437" s="1" t="n">
-        <v>45967.6489236111</v>
+        <v>45968.6659027778</v>
       </c>
       <c r="B437" t="n">
-        <v>1500</v>
+        <v>3600</v>
       </c>
       <c r="C437" t="n">
-        <v>6.48000001907349</v>
+        <v>6.55999994277954</v>
       </c>
       <c r="D437" t="n">
-        <v>6.48000001907349</v>
+        <v>6.46000003814697</v>
       </c>
       <c r="E437" t="n">
         <v>6.48000001907349</v>
       </c>
       <c r="F437" t="n">
-        <v>6.48000001907349</v>
+        <v>6.55999994277954</v>
       </c>
       <c r="G437" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -11995,27 +11995,105 @@
     </row>
     <row r="437">
       <c r="A437" s="1" t="n">
-        <v>45968.6659027778</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B437" t="n">
-        <v>3600</v>
+        <v>12900</v>
       </c>
       <c r="C437" t="n">
-        <v>6.55999994277954</v>
+        <v>6.5</v>
       </c>
       <c r="D437" t="n">
         <v>6.46000003814697</v>
       </c>
       <c r="E437" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F437" t="n">
         <v>6.48000001907349</v>
       </c>
-      <c r="F437" t="n">
+      <c r="G437" t="s">
+        <v>101</v>
+      </c>
+      <c r="H437" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B438" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C438" t="n">
+        <v>6.48000001907349</v>
+      </c>
+      <c r="D438" t="n">
+        <v>6.48000001907349</v>
+      </c>
+      <c r="E438" t="n">
+        <v>6.48000001907349</v>
+      </c>
+      <c r="F438" t="n">
+        <v>6.48000001907349</v>
+      </c>
+      <c r="G438" t="s">
+        <v>101</v>
+      </c>
+      <c r="H438" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B439" t="n">
+        <v>3600</v>
+      </c>
+      <c r="C439" t="n">
         <v>6.55999994277954</v>
       </c>
-      <c r="G437" t="s">
+      <c r="D439" t="n">
+        <v>6.46000003814697</v>
+      </c>
+      <c r="E439" t="n">
+        <v>6.48000001907349</v>
+      </c>
+      <c r="F439" t="n">
+        <v>6.55999994277954</v>
+      </c>
+      <c r="G439" t="s">
         <v>102</v>
       </c>
-      <c r="H437" t="s">
+      <c r="H439" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="n">
+        <v>45971.6811111111</v>
+      </c>
+      <c r="B440" t="n">
+        <v>18600</v>
+      </c>
+      <c r="C440" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="D440" t="n">
+        <v>6.46000003814697</v>
+      </c>
+      <c r="E440" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="F440" t="n">
+        <v>6.46000003814697</v>
+      </c>
+      <c r="G440" t="s">
+        <v>48</v>
+      </c>
+      <c r="H440" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -321,6 +321,9 @@
   </si>
   <si>
     <t xml:space="preserve">6.55999994277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5</t>
   </si>
 </sst>
 </file>
@@ -12073,7 +12076,7 @@
     </row>
     <row r="440">
       <c r="A440" s="1" t="n">
-        <v>45971.6811111111</v>
+        <v>45971.3333333333</v>
       </c>
       <c r="B440" t="n">
         <v>18600</v>
@@ -12094,6 +12097,32 @@
         <v>48</v>
       </c>
       <c r="H440" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="n">
+        <v>45972.6004282407</v>
+      </c>
+      <c r="B441" t="n">
+        <v>4800</v>
+      </c>
+      <c r="C441" t="n">
+        <v>6.51999998092651</v>
+      </c>
+      <c r="D441" t="n">
+        <v>6.44000005722046</v>
+      </c>
+      <c r="E441" t="n">
+        <v>6.44000005722046</v>
+      </c>
+      <c r="F441" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G441" t="s">
+        <v>103</v>
+      </c>
+      <c r="H441" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12102,7 +12102,7 @@
     </row>
     <row r="441">
       <c r="A441" s="1" t="n">
-        <v>45972.6004282407</v>
+        <v>45972.3333333333</v>
       </c>
       <c r="B441" t="n">
         <v>4800</v>
@@ -12123,6 +12123,32 @@
         <v>103</v>
       </c>
       <c r="H441" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="1" t="n">
+        <v>45973.6435532407</v>
+      </c>
+      <c r="B442" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C442" t="n">
+        <v>6.53999996185303</v>
+      </c>
+      <c r="D442" t="n">
+        <v>6.46000003814697</v>
+      </c>
+      <c r="E442" t="n">
+        <v>6.48000001907349</v>
+      </c>
+      <c r="F442" t="n">
+        <v>6.48000001907349</v>
+      </c>
+      <c r="G442" t="s">
+        <v>101</v>
+      </c>
+      <c r="H442" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12128,7 +12128,7 @@
     </row>
     <row r="442">
       <c r="A442" s="1" t="n">
-        <v>45973.6435532407</v>
+        <v>45973.3333333333</v>
       </c>
       <c r="B442" t="n">
         <v>15000</v>
@@ -12149,6 +12149,32 @@
         <v>101</v>
       </c>
       <c r="H442" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="n">
+        <v>45974.667662037</v>
+      </c>
+      <c r="B443" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C443" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="D443" t="n">
+        <v>6.44000005722046</v>
+      </c>
+      <c r="E443" t="n">
+        <v>6.48000001907349</v>
+      </c>
+      <c r="F443" t="n">
+        <v>6.46000003814697</v>
+      </c>
+      <c r="G443" t="s">
+        <v>48</v>
+      </c>
+      <c r="H443" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12154,7 +12154,7 @@
     </row>
     <row r="443">
       <c r="A443" s="1" t="n">
-        <v>45974.667662037</v>
+        <v>45974.3333333333</v>
       </c>
       <c r="B443" t="n">
         <v>18000</v>
@@ -12175,6 +12175,32 @@
         <v>48</v>
       </c>
       <c r="H443" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="1" t="n">
+        <v>45975.6322569444</v>
+      </c>
+      <c r="B444" t="n">
+        <v>14400</v>
+      </c>
+      <c r="C444" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D444" t="n">
+        <v>6.42000007629395</v>
+      </c>
+      <c r="E444" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F444" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G444" t="s">
+        <v>103</v>
+      </c>
+      <c r="H444" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -324,6 +324,9 @@
   </si>
   <si>
     <t xml:space="preserve">6.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59999990463257</t>
   </si>
 </sst>
 </file>
@@ -12180,7 +12183,7 @@
     </row>
     <row r="444">
       <c r="A444" s="1" t="n">
-        <v>45975.6322569444</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B444" t="n">
         <v>14400</v>
@@ -12201,6 +12204,32 @@
         <v>103</v>
       </c>
       <c r="H444" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="n">
+        <v>45978.6665972222</v>
+      </c>
+      <c r="B445" t="n">
+        <v>8400</v>
+      </c>
+      <c r="C445" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="D445" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E445" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F445" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="G445" t="s">
+        <v>104</v>
+      </c>
+      <c r="H445" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12209,7 +12209,7 @@
     </row>
     <row r="445">
       <c r="A445" s="1" t="n">
-        <v>45978.6665972222</v>
+        <v>45978.3333333333</v>
       </c>
       <c r="B445" t="n">
         <v>8400</v>
@@ -12230,6 +12230,32 @@
         <v>104</v>
       </c>
       <c r="H445" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="1" t="n">
+        <v>45979.6692708333</v>
+      </c>
+      <c r="B446" t="n">
+        <v>5700</v>
+      </c>
+      <c r="C446" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="D446" t="n">
+        <v>6.53999996185303</v>
+      </c>
+      <c r="E446" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="F446" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="G446" t="s">
+        <v>104</v>
+      </c>
+      <c r="H446" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12235,7 +12235,7 @@
     </row>
     <row r="446">
       <c r="A446" s="1" t="n">
-        <v>45979.6692708333</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B446" t="n">
         <v>5700</v>
@@ -12256,6 +12256,32 @@
         <v>104</v>
       </c>
       <c r="H446" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="1" t="n">
+        <v>45980.662037037</v>
+      </c>
+      <c r="B447" t="n">
+        <v>12300</v>
+      </c>
+      <c r="C447" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="D447" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="E447" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="F447" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="G447" t="s">
+        <v>104</v>
+      </c>
+      <c r="H447" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="106">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -327,6 +327,9 @@
   </si>
   <si>
     <t xml:space="preserve">6.59999990463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65999984741211</t>
   </si>
 </sst>
 </file>
@@ -12261,7 +12264,7 @@
     </row>
     <row r="447">
       <c r="A447" s="1" t="n">
-        <v>45980.662037037</v>
+        <v>45980.3333333333</v>
       </c>
       <c r="B447" t="n">
         <v>12300</v>
@@ -12282,6 +12285,32 @@
         <v>104</v>
       </c>
       <c r="H447" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="1" t="n">
+        <v>45981.6426041667</v>
+      </c>
+      <c r="B448" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C448" t="n">
+        <v>6.65999984741211</v>
+      </c>
+      <c r="D448" t="n">
+        <v>6.65999984741211</v>
+      </c>
+      <c r="E448" t="n">
+        <v>6.65999984741211</v>
+      </c>
+      <c r="F448" t="n">
+        <v>6.65999984741211</v>
+      </c>
+      <c r="G448" t="s">
+        <v>105</v>
+      </c>
+      <c r="H448" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12290,7 +12290,7 @@
     </row>
     <row r="448">
       <c r="A448" s="1" t="n">
-        <v>45981.6426041667</v>
+        <v>45981.3333333333</v>
       </c>
       <c r="B448" t="n">
         <v>1200</v>
@@ -12311,6 +12311,32 @@
         <v>105</v>
       </c>
       <c r="H448" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="1" t="n">
+        <v>45982.5764814815</v>
+      </c>
+      <c r="B449" t="n">
+        <v>3600</v>
+      </c>
+      <c r="C449" t="n">
+        <v>6.65999984741211</v>
+      </c>
+      <c r="D449" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="E449" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="F449" t="n">
+        <v>6.65999984741211</v>
+      </c>
+      <c r="G449" t="s">
+        <v>105</v>
+      </c>
+      <c r="H449" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12316,7 +12316,7 @@
     </row>
     <row r="449">
       <c r="A449" s="1" t="n">
-        <v>45982.5764814815</v>
+        <v>45982.3333333333</v>
       </c>
       <c r="B449" t="n">
         <v>3600</v>
@@ -12337,6 +12337,32 @@
         <v>105</v>
       </c>
       <c r="H449" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="1" t="n">
+        <v>45985.6472106482</v>
+      </c>
+      <c r="B450" t="n">
+        <v>9300</v>
+      </c>
+      <c r="C450" t="n">
+        <v>6.61999988555908</v>
+      </c>
+      <c r="D450" t="n">
+        <v>6.55999994277954</v>
+      </c>
+      <c r="E450" t="n">
+        <v>6.61999988555908</v>
+      </c>
+      <c r="F450" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="G450" t="s">
+        <v>72</v>
+      </c>
+      <c r="H450" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12342,7 +12342,7 @@
     </row>
     <row r="450">
       <c r="A450" s="1" t="n">
-        <v>45985.6472106482</v>
+        <v>45985.3333333333</v>
       </c>
       <c r="B450" t="n">
         <v>9300</v>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12366,6 +12366,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="451">
+      <c r="A451" s="1" t="n">
+        <v>45986.3333333333</v>
+      </c>
+      <c r="B451" t="n">
+        <v>0</v>
+      </c>
+      <c r="C451" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="D451" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="E451" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="F451" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="G451" t="s">
+        <v>72</v>
+      </c>
+      <c r="H451" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12392,6 +12392,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="452">
+      <c r="A452" s="1" t="n">
+        <v>45987.3333333333</v>
+      </c>
+      <c r="B452" t="n">
+        <v>0</v>
+      </c>
+      <c r="C452" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="D452" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="E452" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="F452" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="G452" t="s">
+        <v>72</v>
+      </c>
+      <c r="H452" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="1" t="n">
+        <v>45988.6824074074</v>
+      </c>
+      <c r="B453" t="n">
+        <v>13800</v>
+      </c>
+      <c r="C453" t="n">
+        <v>6.55999994277954</v>
+      </c>
+      <c r="D453" t="n">
+        <v>6.55999994277954</v>
+      </c>
+      <c r="E453" t="n">
+        <v>6.55999994277954</v>
+      </c>
+      <c r="F453" t="n">
+        <v>6.55999994277954</v>
+      </c>
+      <c r="G453" t="s">
+        <v>102</v>
+      </c>
+      <c r="H453" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12420,7 +12420,7 @@
     </row>
     <row r="453">
       <c r="A453" s="1" t="n">
-        <v>45988.6824074074</v>
+        <v>45988.3333333333</v>
       </c>
       <c r="B453" t="n">
         <v>13800</v>
@@ -12441,6 +12441,32 @@
         <v>102</v>
       </c>
       <c r="H453" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="1" t="n">
+        <v>45989.5721990741</v>
+      </c>
+      <c r="B454" t="n">
+        <v>60300</v>
+      </c>
+      <c r="C454" t="n">
+        <v>6.61999988555908</v>
+      </c>
+      <c r="D454" t="n">
+        <v>6.61999988555908</v>
+      </c>
+      <c r="E454" t="n">
+        <v>6.61999988555908</v>
+      </c>
+      <c r="F454" t="n">
+        <v>6.61999988555908</v>
+      </c>
+      <c r="G454" t="s">
+        <v>81</v>
+      </c>
+      <c r="H454" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12446,7 +12446,7 @@
     </row>
     <row r="454">
       <c r="A454" s="1" t="n">
-        <v>45989.5721990741</v>
+        <v>45989.3333333333</v>
       </c>
       <c r="B454" t="n">
         <v>60300</v>
@@ -12467,6 +12467,32 @@
         <v>81</v>
       </c>
       <c r="H454" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="1" t="n">
+        <v>45992.6631018519</v>
+      </c>
+      <c r="B455" t="n">
+        <v>20100</v>
+      </c>
+      <c r="C455" t="n">
+        <v>6.55999994277954</v>
+      </c>
+      <c r="D455" t="n">
+        <v>6.53999996185303</v>
+      </c>
+      <c r="E455" t="n">
+        <v>6.53999996185303</v>
+      </c>
+      <c r="F455" t="n">
+        <v>6.53999996185303</v>
+      </c>
+      <c r="G455" t="s">
+        <v>83</v>
+      </c>
+      <c r="H455" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12472,7 +12472,7 @@
     </row>
     <row r="455">
       <c r="A455" s="1" t="n">
-        <v>45992.6631018519</v>
+        <v>45992.3333333333</v>
       </c>
       <c r="B455" t="n">
         <v>20100</v>
@@ -12493,6 +12493,32 @@
         <v>83</v>
       </c>
       <c r="H455" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="1" t="n">
+        <v>45993.6811574074</v>
+      </c>
+      <c r="B456" t="n">
+        <v>5100</v>
+      </c>
+      <c r="C456" t="n">
+        <v>6.51999998092651</v>
+      </c>
+      <c r="D456" t="n">
+        <v>6.48000001907349</v>
+      </c>
+      <c r="E456" t="n">
+        <v>6.51999998092651</v>
+      </c>
+      <c r="F456" t="n">
+        <v>6.48000001907349</v>
+      </c>
+      <c r="G456" t="s">
+        <v>101</v>
+      </c>
+      <c r="H456" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12498,7 +12498,7 @@
     </row>
     <row r="456">
       <c r="A456" s="1" t="n">
-        <v>45993.6811574074</v>
+        <v>45993.3333333333</v>
       </c>
       <c r="B456" t="n">
         <v>5100</v>
@@ -12519,6 +12519,32 @@
         <v>101</v>
       </c>
       <c r="H456" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="1" t="n">
+        <v>45994.6912152778</v>
+      </c>
+      <c r="B457" t="n">
+        <v>59100</v>
+      </c>
+      <c r="C457" t="n">
+        <v>6.51999998092651</v>
+      </c>
+      <c r="D457" t="n">
+        <v>6.48000001907349</v>
+      </c>
+      <c r="E457" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F457" t="n">
+        <v>6.51999998092651</v>
+      </c>
+      <c r="G457" t="s">
+        <v>70</v>
+      </c>
+      <c r="H457" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12524,7 +12524,7 @@
     </row>
     <row r="457">
       <c r="A457" s="1" t="n">
-        <v>45994.6912152778</v>
+        <v>45994.3333333333</v>
       </c>
       <c r="B457" t="n">
         <v>59100</v>
@@ -12545,6 +12545,32 @@
         <v>70</v>
       </c>
       <c r="H457" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="1" t="n">
+        <v>45995.5488425926</v>
+      </c>
+      <c r="B458" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C458" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D458" t="n">
+        <v>6.46000003814697</v>
+      </c>
+      <c r="E458" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F458" t="n">
+        <v>6.46000003814697</v>
+      </c>
+      <c r="G458" t="s">
+        <v>48</v>
+      </c>
+      <c r="H458" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12550,7 +12550,7 @@
     </row>
     <row r="458">
       <c r="A458" s="1" t="n">
-        <v>45995.5488425926</v>
+        <v>45995.3333333333</v>
       </c>
       <c r="B458" t="n">
         <v>1500</v>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12574,6 +12574,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="459">
+      <c r="A459" s="1" t="n">
+        <v>45996.3333333333</v>
+      </c>
+      <c r="B459" t="n">
+        <v>0</v>
+      </c>
+      <c r="C459" t="n">
+        <v>6.46000003814697</v>
+      </c>
+      <c r="D459" t="n">
+        <v>6.46000003814697</v>
+      </c>
+      <c r="E459" t="n">
+        <v>6.46000003814697</v>
+      </c>
+      <c r="F459" t="n">
+        <v>6.46000003814697</v>
+      </c>
+      <c r="G459" t="s">
+        <v>48</v>
+      </c>
+      <c r="H459" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="1" t="n">
+        <v>45999.6715277778</v>
+      </c>
+      <c r="B460" t="n">
+        <v>336300</v>
+      </c>
+      <c r="C460" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="D460" t="n">
+        <v>6.55999994277954</v>
+      </c>
+      <c r="E460" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="F460" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="G460" t="s">
+        <v>104</v>
+      </c>
+      <c r="H460" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12602,7 +12602,7 @@
     </row>
     <row r="460">
       <c r="A460" s="1" t="n">
-        <v>45999.6715277778</v>
+        <v>45999.3333333333</v>
       </c>
       <c r="B460" t="n">
         <v>336300</v>
@@ -12623,6 +12623,32 @@
         <v>104</v>
       </c>
       <c r="H460" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="1" t="n">
+        <v>46000.5811574074</v>
+      </c>
+      <c r="B461" t="n">
+        <v>16200</v>
+      </c>
+      <c r="C461" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="D461" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="E461" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="F461" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="G461" t="s">
+        <v>72</v>
+      </c>
+      <c r="H461" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12628,7 +12628,7 @@
     </row>
     <row r="461">
       <c r="A461" s="1" t="n">
-        <v>46000.5811574074</v>
+        <v>46000.3333333333</v>
       </c>
       <c r="B461" t="n">
         <v>16200</v>
@@ -12649,6 +12649,32 @@
         <v>72</v>
       </c>
       <c r="H461" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="1" t="n">
+        <v>46001.6767708333</v>
+      </c>
+      <c r="B462" t="n">
+        <v>21600</v>
+      </c>
+      <c r="C462" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="D462" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="E462" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="F462" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="G462" t="s">
+        <v>72</v>
+      </c>
+      <c r="H462" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12654,7 +12654,7 @@
     </row>
     <row r="462">
       <c r="A462" s="1" t="n">
-        <v>46001.6767708333</v>
+        <v>46001.3333333333</v>
       </c>
       <c r="B462" t="n">
         <v>21600</v>
@@ -12675,6 +12675,32 @@
         <v>72</v>
       </c>
       <c r="H462" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="1" t="n">
+        <v>46002.5866782407</v>
+      </c>
+      <c r="B463" t="n">
+        <v>7500</v>
+      </c>
+      <c r="C463" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="D463" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="E463" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="F463" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="G463" t="s">
+        <v>72</v>
+      </c>
+      <c r="H463" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12680,7 +12680,7 @@
     </row>
     <row r="463">
       <c r="A463" s="1" t="n">
-        <v>46002.5866782407</v>
+        <v>46002.3333333333</v>
       </c>
       <c r="B463" t="n">
         <v>7500</v>
@@ -12701,6 +12701,32 @@
         <v>72</v>
       </c>
       <c r="H463" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="1" t="n">
+        <v>46003.6911111111</v>
+      </c>
+      <c r="B464" t="n">
+        <v>19800</v>
+      </c>
+      <c r="C464" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="D464" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="E464" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="F464" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="G464" t="s">
+        <v>104</v>
+      </c>
+      <c r="H464" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12706,13 +12706,13 @@
     </row>
     <row r="464">
       <c r="A464" s="1" t="n">
-        <v>46003.6911111111</v>
+        <v>46003.3333333333</v>
       </c>
       <c r="B464" t="n">
         <v>19800</v>
       </c>
       <c r="C464" t="n">
-        <v>6.57999992370605</v>
+        <v>6.59999990463257</v>
       </c>
       <c r="D464" t="n">
         <v>6.57999992370605</v>
@@ -12727,6 +12727,32 @@
         <v>104</v>
       </c>
       <c r="H464" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="1" t="n">
+        <v>46006.6910300926</v>
+      </c>
+      <c r="B465" t="n">
+        <v>91800</v>
+      </c>
+      <c r="C465" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="D465" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="E465" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="F465" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="G465" t="s">
+        <v>72</v>
+      </c>
+      <c r="H465" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12732,7 +12732,7 @@
     </row>
     <row r="465">
       <c r="A465" s="1" t="n">
-        <v>46006.6910300926</v>
+        <v>46006.3333333333</v>
       </c>
       <c r="B465" t="n">
         <v>91800</v>
@@ -12753,6 +12753,32 @@
         <v>72</v>
       </c>
       <c r="H465" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="1" t="n">
+        <v>46007.6910069444</v>
+      </c>
+      <c r="B466" t="n">
+        <v>82200</v>
+      </c>
+      <c r="C466" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="D466" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="E466" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="F466" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="G466" t="s">
+        <v>72</v>
+      </c>
+      <c r="H466" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12758,7 +12758,7 @@
     </row>
     <row r="466">
       <c r="A466" s="1" t="n">
-        <v>46007.6910069444</v>
+        <v>46007.3333333333</v>
       </c>
       <c r="B466" t="n">
         <v>82200</v>
@@ -12779,6 +12779,32 @@
         <v>72</v>
       </c>
       <c r="H466" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="1" t="n">
+        <v>46008.5549884259</v>
+      </c>
+      <c r="B467" t="n">
+        <v>27000</v>
+      </c>
+      <c r="C467" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="D467" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="E467" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="F467" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="G467" t="s">
+        <v>72</v>
+      </c>
+      <c r="H467" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12784,7 +12784,7 @@
     </row>
     <row r="467">
       <c r="A467" s="1" t="n">
-        <v>46008.5549884259</v>
+        <v>46008.3333333333</v>
       </c>
       <c r="B467" t="n">
         <v>27000</v>
@@ -12805,6 +12805,32 @@
         <v>72</v>
       </c>
       <c r="H467" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="1" t="n">
+        <v>46009.5889814815</v>
+      </c>
+      <c r="B468" t="n">
+        <v>9300</v>
+      </c>
+      <c r="C468" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="D468" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="E468" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="F468" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="G468" t="s">
+        <v>72</v>
+      </c>
+      <c r="H468" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12810,7 +12810,7 @@
     </row>
     <row r="468">
       <c r="A468" s="1" t="n">
-        <v>46009.5889814815</v>
+        <v>46009.3333333333</v>
       </c>
       <c r="B468" t="n">
         <v>9300</v>
@@ -12831,6 +12831,32 @@
         <v>72</v>
       </c>
       <c r="H468" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="1" t="n">
+        <v>46010.6826967593</v>
+      </c>
+      <c r="B469" t="n">
+        <v>40200</v>
+      </c>
+      <c r="C469" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="D469" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="E469" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="F469" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="G469" t="s">
+        <v>72</v>
+      </c>
+      <c r="H469" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12836,7 +12836,7 @@
     </row>
     <row r="469">
       <c r="A469" s="1" t="n">
-        <v>46010.6826967593</v>
+        <v>46010.3333333333</v>
       </c>
       <c r="B469" t="n">
         <v>40200</v>
@@ -12857,6 +12857,32 @@
         <v>72</v>
       </c>
       <c r="H469" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="1" t="n">
+        <v>46013.6165856482</v>
+      </c>
+      <c r="B470" t="n">
+        <v>900</v>
+      </c>
+      <c r="C470" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="D470" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="E470" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="F470" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="G470" t="s">
+        <v>72</v>
+      </c>
+      <c r="H470" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12862,7 +12862,7 @@
     </row>
     <row r="470">
       <c r="A470" s="1" t="n">
-        <v>46013.6165856482</v>
+        <v>46013.3333333333</v>
       </c>
       <c r="B470" t="n">
         <v>900</v>
@@ -12883,6 +12883,32 @@
         <v>72</v>
       </c>
       <c r="H470" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="1" t="n">
+        <v>46014.6858449074</v>
+      </c>
+      <c r="B471" t="n">
+        <v>900</v>
+      </c>
+      <c r="C471" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="D471" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="E471" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="F471" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="G471" t="s">
+        <v>72</v>
+      </c>
+      <c r="H471" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12888,7 +12888,7 @@
     </row>
     <row r="471">
       <c r="A471" s="1" t="n">
-        <v>46014.6858449074</v>
+        <v>46014.3333333333</v>
       </c>
       <c r="B471" t="n">
         <v>900</v>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12912,6 +12912,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="472">
+      <c r="A472" s="1" t="n">
+        <v>46020.6861574074</v>
+      </c>
+      <c r="B472" t="n">
+        <v>3900</v>
+      </c>
+      <c r="C472" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="D472" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="E472" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="F472" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="G472" t="s">
+        <v>72</v>
+      </c>
+      <c r="H472" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12914,7 +12914,7 @@
     </row>
     <row r="472">
       <c r="A472" s="1" t="n">
-        <v>46020.6861574074</v>
+        <v>46020.3333333333</v>
       </c>
       <c r="B472" t="n">
         <v>3900</v>
@@ -12935,6 +12935,32 @@
         <v>72</v>
       </c>
       <c r="H472" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="1" t="n">
+        <v>46021.6302083333</v>
+      </c>
+      <c r="B473" t="n">
+        <v>11700</v>
+      </c>
+      <c r="C473" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="D473" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="E473" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="F473" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="G473" t="s">
+        <v>104</v>
+      </c>
+      <c r="H473" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12940,7 +12940,7 @@
     </row>
     <row r="473">
       <c r="A473" s="1" t="n">
-        <v>46021.6302083333</v>
+        <v>46021.3333333333</v>
       </c>
       <c r="B473" t="n">
         <v>11700</v>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12964,6 +12964,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="474">
+      <c r="A474" s="1" t="n">
+        <v>46024.3333333333</v>
+      </c>
+      <c r="B474" t="n">
+        <v>0</v>
+      </c>
+      <c r="C474" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="D474" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="E474" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="F474" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="G474" t="s">
+        <v>104</v>
+      </c>
+      <c r="H474" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="1" t="n">
+        <v>46027.4961921296</v>
+      </c>
+      <c r="B475" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C475" t="n">
+        <v>6.61999988555908</v>
+      </c>
+      <c r="D475" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="E475" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="F475" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="G475" t="s">
+        <v>104</v>
+      </c>
+      <c r="H475" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -12992,7 +12992,7 @@
     </row>
     <row r="475">
       <c r="A475" s="1" t="n">
-        <v>46027.4961921296</v>
+        <v>46027.3333333333</v>
       </c>
       <c r="B475" t="n">
         <v>2400</v>
@@ -13013,6 +13013,32 @@
         <v>104</v>
       </c>
       <c r="H475" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="1" t="n">
+        <v>46028.6849421296</v>
+      </c>
+      <c r="B476" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C476" t="n">
+        <v>6.61999988555908</v>
+      </c>
+      <c r="D476" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="E476" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="F476" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="G476" t="s">
+        <v>104</v>
+      </c>
+      <c r="H476" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -13018,10 +13018,10 @@
     </row>
     <row r="476">
       <c r="A476" s="1" t="n">
-        <v>46028.6849421296</v>
+        <v>46028.3333333333</v>
       </c>
       <c r="B476" t="n">
-        <v>1800</v>
+        <v>8400</v>
       </c>
       <c r="C476" t="n">
         <v>6.61999988555908</v>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -13042,6 +13042,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="477">
+      <c r="A477" s="1" t="n">
+        <v>46029.3333333333</v>
+      </c>
+      <c r="B477" t="n">
+        <v>0</v>
+      </c>
+      <c r="C477" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="D477" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="E477" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="F477" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="G477" t="s">
+        <v>104</v>
+      </c>
+      <c r="H477" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PAL.MI.xlsx
+++ b/data/PAL.MI.xlsx
@@ -13068,6 +13068,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="478">
+      <c r="A478" s="1" t="n">
+        <v>46030.3333333333</v>
+      </c>
+      <c r="B478" t="n">
+        <v>0</v>
+      </c>
+      <c r="C478" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="D478" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="E478" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="F478" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="G478" t="s">
+        <v>104</v>
+      </c>
+      <c r="H478" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
